--- a/TailCircle-Work-Checklist.xlsx
+++ b/TailCircle-Work-Checklist.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2369,7 +2369,7 @@
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>USER ACTIVITY TRACKING &amp; COOKIES - NOT STARTED</t>
+          <t>USER ACTIVITY TRACKING &amp; COOKIES - BUILT</t>
         </is>
       </c>
       <c r="B108" s="6" t="n"/>
@@ -2382,15 +2382,15 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Cookie consent banner and cookie policy</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D109" s="13">
+          <t>Cookie consent banner shown on a visitor's first arrival</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D109" s="11">
         <f>IF(C109="Done","✓","–")</f>
         <v/>
       </c>
@@ -2401,15 +2401,15 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Track customer activity across the app - screens visited and time spent</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D110" s="13">
+          <t>Accept and Decline given equal prominence - closing the banner counts as decline</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D110" s="11">
         <f>IF(C110="Done","✓","–")</f>
         <v/>
       </c>
@@ -2420,15 +2420,15 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Track what customers search for</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D111" s="13">
+          <t>Declining means NO tracking at all, not anonymous tracking</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D111" s="11">
         <f>IF(C111="Done","✓","–")</f>
         <v/>
       </c>
@@ -2439,15 +2439,15 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Track what customers view but do not book</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D112" s="13">
+          <t>Privacy &amp; Cookies screen so customers can change their mind later</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D112" s="11">
         <f>IF(C112="Done","✓","–")</f>
         <v/>
       </c>
@@ -2458,15 +2458,15 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Record session length and how often a customer returns</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D113" s="13">
+          <t>Withdrawing consent deletes everything already collected</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D113" s="11">
         <f>IF(C113="Done","✓","–")</f>
         <v/>
       </c>
@@ -2477,15 +2477,15 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Admin screen to view an individual customer's activity and journey</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D114" s="13">
+          <t>Track customer activity across the app - screens visited and time spent</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D114" s="11">
         <f>IF(C114="Done","✓","–")</f>
         <v/>
       </c>
@@ -2496,15 +2496,15 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Report on most viewed services, products and categories</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D115" s="13">
+          <t>Track what customers search for, with how many results they got</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D115" s="11">
         <f>IF(C115="Done","✓","–")</f>
         <v/>
       </c>
@@ -2515,15 +2515,15 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Browse-to-booking conversion funnel - where customers drop off</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D116" s="13">
+          <t>Track which services and products customers view, and for how long</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D116" s="11">
         <f>IF(C116="Done","✓","–")</f>
         <v/>
       </c>
@@ -2534,15 +2534,15 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Report on which city / area customers are browsing from</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D117" s="13">
+          <t>Record session length and how often a customer returns</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D117" s="11">
         <f>IF(C117="Done","✓","–")</f>
         <v/>
       </c>
@@ -2553,180 +2553,180 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Admin dashboard section for customer behaviour insights</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D118" s="13">
+          <t>Admin screen to view an individual customer's activity and journey</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D118" s="11">
         <f>IF(C118="Done","✓","–")</f>
         <v/>
       </c>
     </row>
-    <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>IN PROGRESS / NEXT UP</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="7" t="n"/>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Report on most viewed services, products and categories</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D119" s="11">
+        <f>IF(C119="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Report on what customers viewed but did not book</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D120" s="11">
+        <f>IF(C120="Done","✓","–")</f>
+        <v/>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="8" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Admin screen to resolve customer disputes</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D121" s="13">
+          <t>Browse-to-booking conversion funnel - shows the biggest drop-off point</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D121" s="11">
         <f>IF(C121="Done","✓","–")</f>
         <v/>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="8" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Hold partner payout while a booking is disputed</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D122" s="13">
+          <t>Report on which city / area customers are browsing from</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D122" s="11">
         <f>IF(C122="Done","✓","–")</f>
         <v/>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="8" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Reassign bookings automatically when a partner is suspended</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D123" s="13">
+          <t>Customer Behaviour page added to the Admin panel</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D123" s="11">
         <f>IF(C123="Done","✓","–")</f>
         <v/>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="8" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Admin toggle to turn manual booking acceptance on per partner</t>
-        </is>
-      </c>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D124" s="13">
+          <t>Opt-in rate shown on every report, so figures are read in context</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D124" s="11">
         <f>IF(C124="Done","✓","–")</f>
         <v/>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Written permissions matrix - who can do what</t>
-        </is>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D125" s="13">
+          <t>Search terms returning no results flagged - demand the catalogue misses</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D125" s="11">
         <f>IF(C125="Done","✓","–")</f>
         <v/>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="8" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Daily payment gateway reconciliation report</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D126" s="13">
+          <t>Personal data in web addresses is stripped before anything is stored</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D126" s="11">
         <f>IF(C126="Done","✓","–")</f>
         <v/>
       </c>
     </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>Chargeback / payment reversal handling</t>
-        </is>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D127" s="13">
-        <f>IF(C127="Done","✓","–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>Automatic retry for failed notifications</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D128" s="13">
-        <f>IF(C128="Done","✓","–")</f>
-        <v/>
-      </c>
+    <row r="128" ht="26" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>DISPUTES &amp; PARTNER ACCOUNTABILITY</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="7" t="n"/>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="8" t="n">
@@ -2734,15 +2734,15 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Coupons and discount codes</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D129" s="13">
+          <t>Admin screen to review and rule on customer disputes</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D129" s="11">
         <f>IF(C129="Done","✓","–")</f>
         <v/>
       </c>
@@ -2753,15 +2753,15 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Service area management</t>
-        </is>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D130" s="13">
+          <t>Four clear outcomes - full refund, partial refund, reject, or refund without fault</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D130" s="11">
         <f>IF(C130="Done","✓","–")</f>
         <v/>
       </c>
@@ -2772,15 +2772,15 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Emergency request queue for Admin</t>
-        </is>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D131" s="13">
+          <t>Resolution always states what happens to the customer's money</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D131" s="11">
         <f>IF(C131="Done","✓","–")</f>
         <v/>
       </c>
@@ -2791,15 +2791,15 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Partner response-time leaderboard</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D132" s="13">
+          <t>Written reason required, and the customer is told what was decided</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D132" s="11">
         <f>IF(C132="Done","✓","–")</f>
         <v/>
       </c>
@@ -2810,15 +2810,15 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Low stock alerts</t>
-        </is>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D133" s="13">
+          <t>Partner earnings are HELD from payout while a booking is disputed</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D133" s="11">
         <f>IF(C133="Done","✓","–")</f>
         <v/>
       </c>
@@ -2829,44 +2829,696 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Duplicate booking detection</t>
-        </is>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
+          <t>Payout document shows what was held and why</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D134" s="11">
+        <f>IF(C134="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>Hold releases automatically once the dispute is resolved</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D135" s="11">
+        <f>IF(C135="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>Upheld disputes record a service failure against the partner</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D136" s="11">
+        <f>IF(C136="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>Queue sorted oldest-first, flagging anything open over a week</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D137" s="11">
+        <f>IF(C137="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" ht="26" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>OPERATIONAL QUEUES - NEW ADMIN SCREEN</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="7" t="n"/>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>Live emergency requests queue, flagging anything unanswered over 15 minutes</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D140" s="11">
+        <f>IF(C140="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Customers stranded when a partner is suspended - shows who is still owed a service</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D141" s="11">
+        <f>IF(C141="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate booking detection - catches customers charged twice for one intention</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D142" s="11">
+        <f>IF(C142="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>Partner response-time leaderboard, worst responders first</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D143" s="11">
+        <f>IF(C143="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>Unanswered requests counted against partners, not just slow ones</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D144" s="11">
+        <f>IF(C144="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Low stock and out-of-stock alerts per product size</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D145" s="11">
+        <f>IF(C145="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>MONEY SAFETY</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n"/>
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="7" t="n"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>Daily reconciliation report - checks the platform's records against themselves</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D148" s="11">
+        <f>IF(C148="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>Flags customers charged where the booking or order never confirmed</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D149" s="11">
+        <f>IF(C149="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>Flags refunds with no record of who authorised them</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D150" s="11">
+        <f>IF(C150="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>Flags customers refunded where the partner was not clawed back</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D151" s="11">
+        <f>IF(C151="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>Flags refunds that failed - customers still owed money</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D152" s="11">
+        <f>IF(C152="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Flags payments confirmed by the browser but never verified by the gateway</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D153" s="11">
+        <f>IF(C153="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>Flags partners credited with no payment behind it</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D154" s="11">
+        <f>IF(C154="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" ht="26" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>PARTNER &amp; PLATFORM CONTROLS</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="n"/>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="7" t="n"/>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>Admin toggle to switch a partner to manual booking acceptance</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D157" s="11">
+        <f>IF(C157="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>Partner is notified when their acceptance mode changes, with the consequences</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D158" s="11">
+        <f>IF(C158="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>Failed notifications now retried automatically every 15 minutes</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D159" s="11">
+        <f>IF(C159="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>Retry capped so a permanently dead device is not retried forever</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D160" s="11">
+        <f>IF(C160="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>Admin can trigger a notification retry on demand</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D161" s="11">
+        <f>IF(C161="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>Service area management - define where the platform operates, by pincode</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D162" s="11">
+        <f>IF(C162="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>A pincode can belong to only one area, so serviceability is never ambiguous</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D163" s="11">
+        <f>IF(C163="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>Areas can be paused without losing their pincode list</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D164" s="11">
+        <f>IF(C164="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>Per-vertical launch - grooming can be live in an area before daycare</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D165" s="11">
+        <f>IF(C165="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>Written permissions matrix documenting who can do what</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D166" s="11">
+        <f>IF(C166="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="26" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>STILL TO DO</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="n"/>
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="7" t="n"/>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>Coupons and discount codes - needs scope agreed with client</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="D134" s="13">
-        <f>IF(C134="Done","✓","–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="14" t="inlineStr">
+      <c r="D169" s="13">
+        <f>IF(C169="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>Chargeback / payment reversal handling - needs Razorpay dispute webhooks enabled</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D170" s="13">
+        <f>IF(C170="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>Customer compensation credits on partner-caused failures</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D171" s="13">
+        <f>IF(C171="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>Finer-grained admin roles (ops / finance / support are stored but not enforced)</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D172" s="13">
+        <f>IF(C172="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>Customer data export and account deletion</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D173" s="13">
+        <f>IF(C173="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>Wire service areas into customer-facing search and checkout</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D174" s="13">
+        <f>IF(C174="Done","✓","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="14" t="inlineStr">
         <is>
           <t>All completed items have been tested and verified on the development environment.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="17">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A93:D93"/>
-    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="A168:D168"/>
+    <mergeCell ref="A139:D139"/>
     <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A147:D147"/>
+    <mergeCell ref="A156:D156"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A137:D137"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A177:D177"/>
     <mergeCell ref="A84:D84"/>
     <mergeCell ref="A108:D108"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C18 C19 C20 C21 C22 C23 C24 C25 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C64 C65 C66 C67 C68 C69 C70 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C85 C86 C87 C88 C89 C90 C91 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C131 C132 C133 C134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C18 C19 C20 C21 C22 C23 C24 C25 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C64 C65 C66 C67 C68 C69 C70 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C85 C86 C87 C88 C89 C90 C91 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C119 C120 C121 C122 C123 C124 C125 C126 C129 C130 C131 C132 C133 C134 C135 C136 C137 C140 C141 C142 C143 C144 C145 C148 C149 C150 C151 C152 C153 C154 C157 C158 C159 C160 C161 C162 C163 C164 C165 C166 C169 C170 C171 C172 C173 C174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Done,Pending"</formula1>
     </dataValidation>
   </dataValidations>
